--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N114_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N114_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.85420002753579</v>
+        <v>8.751307504474566</v>
       </c>
       <c r="D2" t="n">
-        <v>51.21637612282463</v>
+        <v>8.322661119959003</v>
       </c>
       <c r="E2" t="n">
-        <v>11.5870749637758</v>
+        <v>1.882899681613567</v>
       </c>
       <c r="F2" t="n">
-        <v>11.4356864442498</v>
+        <v>1.858299047190593</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.82597358203995</v>
+        <v>7.446720707081492</v>
       </c>
       <c r="D3" t="n">
-        <v>44.31543373435876</v>
+        <v>7.201257981833299</v>
       </c>
       <c r="E3" t="n">
-        <v>11.5870749637758</v>
+        <v>1.882899681613567</v>
       </c>
       <c r="F3" t="n">
-        <v>11.4356864442498</v>
+        <v>1.858299047190593</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.8621630293869</v>
+        <v>6.315101492275371</v>
       </c>
       <c r="D4" t="n">
-        <v>37.32133782792009</v>
+        <v>6.064717397037015</v>
       </c>
       <c r="E4" t="n">
-        <v>11.5870749637758</v>
+        <v>1.882899681613567</v>
       </c>
       <c r="F4" t="n">
-        <v>11.4356864442498</v>
+        <v>1.858299047190593</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.16185792135404</v>
+        <v>5.063801912220032</v>
       </c>
       <c r="D5" t="n">
-        <v>28.5928916405273</v>
+        <v>4.646344891585686</v>
       </c>
       <c r="E5" t="n">
-        <v>11.5870749637758</v>
+        <v>1.882899681613567</v>
       </c>
       <c r="F5" t="n">
-        <v>11.4356864442498</v>
+        <v>1.858299047190593</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.35336628671072</v>
+        <v>4.119922021590492</v>
       </c>
       <c r="D6" t="n">
-        <v>23.61113124967778</v>
+        <v>3.836808828072638</v>
       </c>
       <c r="E6" t="n">
-        <v>11.5870749637758</v>
+        <v>1.882899681613567</v>
       </c>
       <c r="F6" t="n">
-        <v>11.4356864442498</v>
+        <v>1.858299047190593</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>24.83887058880649</v>
+        <v>4.036316470681054</v>
       </c>
       <c r="D7" t="n">
-        <v>22.18357243353607</v>
+        <v>3.604830520449612</v>
       </c>
       <c r="E7" t="n">
-        <v>11.5870749637758</v>
+        <v>1.882899681613567</v>
       </c>
       <c r="F7" t="n">
-        <v>11.4356864442498</v>
+        <v>1.858299047190593</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.1229986088615</v>
+        <v>6.032487273939994</v>
       </c>
       <c r="D8" t="n">
-        <v>36.86356206839999</v>
+        <v>5.990328836114998</v>
       </c>
       <c r="E8" t="n">
-        <v>11.5870749637758</v>
+        <v>1.882899681613567</v>
       </c>
       <c r="F8" t="n">
-        <v>11.4356864442498</v>
+        <v>1.858299047190593</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>21.98629517034087</v>
+        <v>3.572772965180391</v>
       </c>
       <c r="D9" t="n">
-        <v>22.90835776709005</v>
+        <v>3.722608137152134</v>
       </c>
       <c r="E9" t="n">
-        <v>11.5870749637758</v>
+        <v>1.882899681613567</v>
       </c>
       <c r="F9" t="n">
-        <v>11.4356864442498</v>
+        <v>1.858299047190593</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>26.12190931652113</v>
+        <v>4.244810263934683</v>
       </c>
       <c r="D10" t="n">
-        <v>25.26346321081889</v>
+        <v>4.10531277175807</v>
       </c>
       <c r="E10" t="n">
-        <v>11.5870749637758</v>
+        <v>1.882899681613567</v>
       </c>
       <c r="F10" t="n">
-        <v>11.4356864442498</v>
+        <v>1.858299047190593</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>2.719731643686566</v>
+        <v>0.441956392099067</v>
       </c>
       <c r="D11" t="n">
-        <v>5.473870312036539</v>
+        <v>0.8895039257059375</v>
       </c>
       <c r="E11" t="n">
-        <v>11.5870749637758</v>
+        <v>1.882899681613567</v>
       </c>
       <c r="F11" t="n">
-        <v>11.4356864442498</v>
+        <v>1.858299047190593</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>33.60099837491347</v>
+        <v>5.460162235923439</v>
       </c>
       <c r="D12" t="n">
-        <v>34.99671943475539</v>
+        <v>5.686966908147752</v>
       </c>
       <c r="E12" t="n">
-        <v>11.5870749637758</v>
+        <v>1.882899681613567</v>
       </c>
       <c r="F12" t="n">
-        <v>11.4356864442498</v>
+        <v>1.858299047190593</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>43.23461464083352</v>
+        <v>7.025624879135448</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26705055458775</v>
+        <v>7.355895715120511</v>
       </c>
       <c r="E13" t="n">
-        <v>11.5870749637758</v>
+        <v>1.882899681613567</v>
       </c>
       <c r="F13" t="n">
-        <v>11.4356864442498</v>
+        <v>1.858299047190593</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>27.07719215579753</v>
+        <v>4.400043725317099</v>
       </c>
       <c r="D14" t="n">
-        <v>24.78780988408382</v>
+        <v>4.028019106163621</v>
       </c>
       <c r="E14" t="n">
-        <v>11.5870749637758</v>
+        <v>1.882899681613567</v>
       </c>
       <c r="F14" t="n">
-        <v>11.4356864442498</v>
+        <v>1.858299047190593</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>37.51971967450181</v>
+        <v>6.096954447106545</v>
       </c>
       <c r="D15" t="n">
-        <v>30.69100778503249</v>
+        <v>4.98728876506778</v>
       </c>
       <c r="E15" t="n">
-        <v>11.5870749637758</v>
+        <v>1.882899681613567</v>
       </c>
       <c r="F15" t="n">
-        <v>11.4356864442498</v>
+        <v>1.858299047190593</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>32.45021528754467</v>
+        <v>5.273159984226008</v>
       </c>
       <c r="D16" t="n">
-        <v>18.07668215755664</v>
+        <v>2.937460850602954</v>
       </c>
       <c r="E16" t="n">
-        <v>11.5870749637758</v>
+        <v>1.882899681613567</v>
       </c>
       <c r="F16" t="n">
-        <v>11.4356864442498</v>
+        <v>1.858299047190593</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
